--- a/database.xlsx
+++ b/database.xlsx
@@ -6,6 +6,9 @@
     <sheet name="Pemain" sheetId="1" r:id="rId1"/>
     <sheet name="Klub" sheetId="2" r:id="rId2"/>
     <sheet name="Wasit" sheetId="3" r:id="rId3"/>
+    <sheet name="Turnamen" sheetId="4" r:id="rId4"/>
+    <sheet name="Lapangan" sheetId="5" r:id="rId5"/>
+    <sheet name="NoPartai" sheetId="6" r:id="rId6"/>
   </sheets>
 </workbook>
 </file>
@@ -399,7 +402,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -426,9 +429,14 @@
         <v>BELVA HUWALDA CARISSA</v>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>FARHAN JEZANDO WARDANA</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:A5"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:A6"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -471,36 +479,88 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:A3"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Nama Wasit</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>Farhan</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>Farhan Jezando Wardana</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:A3"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:A3"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Nama Turnamen</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>Pupuk Kaltim Open 2025</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>sg</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:A3"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:A6"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>Nama Wasit</v>
+        <v>Nama Lapangan</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>asdasdas</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Farasd</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>FITRIAH</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>mmmmm</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>ZAKARIA</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -508,4 +568,35 @@
     <ignoredError numberStoredAsText="1" sqref="A1:A6"/>
   </ignoredErrors>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:A4"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>No. Partai</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>QF-1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>SF-1</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:A4"/>
+  </ignoredErrors>
+</worksheet>
 </file>
--- a/database.xlsx
+++ b/database.xlsx
@@ -479,7 +479,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A2"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -491,21 +491,16 @@
         <v>Farhan</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>Farhan Jezando Wardana</v>
-      </c>
-    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:A3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:A2"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A2"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -514,17 +509,12 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Pupuk Kaltim Open 2025</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>sg</v>
+        <v>Pupuk Kaltim Open 2026</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:A3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:A2"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/database.xlsx
+++ b/database.xlsx
@@ -562,7 +562,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A4"/>
+  <dimension ref="A1:A3"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -571,22 +571,17 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>3</v>
+        <v>QF-1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>QF-1</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
         <v>SF-1</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:A4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:A3"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/database.xlsx
+++ b/database.xlsx
@@ -6,9 +6,10 @@
     <sheet name="Pemain" sheetId="1" r:id="rId1"/>
     <sheet name="Klub" sheetId="2" r:id="rId2"/>
     <sheet name="Wasit" sheetId="3" r:id="rId3"/>
-    <sheet name="Turnamen" sheetId="4" r:id="rId4"/>
-    <sheet name="Lapangan" sheetId="5" r:id="rId5"/>
-    <sheet name="NoPartai" sheetId="6" r:id="rId6"/>
+    <sheet name="ServiceJudge" sheetId="4" r:id="rId4"/>
+    <sheet name="Turnamen" sheetId="5" r:id="rId5"/>
+    <sheet name="Lapangan" sheetId="6" r:id="rId6"/>
+    <sheet name="NoPartai" sheetId="7" r:id="rId7"/>
   </sheets>
 </workbook>
 </file>
@@ -479,7 +480,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A13"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -488,19 +489,170 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Farhan</v>
+        <v>Agam</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>Anis Firdaus</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>Annes Faisal</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>Dian Asrori</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>Ferry Anggriawan</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>Fikri</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>Furqon</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>Lucky Zulkarnain</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>Ndari Wahyu</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>Robi Wisnu</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>Ronny Azhari</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>Wardana</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:A2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:A13"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A17"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Nama Service Judge</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>Ali</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>Alis</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>Alwi</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>Arifin</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>Badarudin</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>Gagah</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>Haris</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>Hermawan</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>Iban</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>Lukman</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>Nanang</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>Rudi</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>Samsul</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>Septian</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>Syafi'i</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>Yusri</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:A17"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:A3"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -509,19 +661,24 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Pupuk Kaltim Open 2026</v>
+        <v>Pupuk Kaltim Open 2026: Gor Alamanda</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>Pupuk Kaltim Open 2026: Gor Graha Cipta Korsa</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:A2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:A3"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A5"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -548,19 +705,14 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>5</v>
-      </c>
-    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:A6"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:A5"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:A3"/>
   <sheetData>

--- a/database.xlsx
+++ b/database.xlsx
@@ -1,7 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://365mic-my.sharepoint.com/personal/ipanjez_365mic_onmicrosoft_com/Documents/Learn/Coding/Badminton/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="2" documentId="11_5ABB27F3C9B0B11E6AFFA0642FBCD094970865D7" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D8B0BA74-F477-47AE-8E27-7C28FA8DFF70}"/>
+  <bookViews>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
     <sheet name="Pemain" sheetId="1" r:id="rId1"/>
     <sheet name="Klub" sheetId="2" r:id="rId2"/>
@@ -11,37 +21,174 @@
     <sheet name="Lapangan" sheetId="6" r:id="rId6"/>
     <sheet name="NoPartai" sheetId="7" r:id="rId7"/>
   </sheets>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="52">
+  <si>
+    <t>Nama Pemain</t>
+  </si>
+  <si>
+    <t>ALISA AMELIA DANSACH</t>
+  </si>
+  <si>
+    <t>ALYA MUHKBITA SARI</t>
+  </si>
+  <si>
+    <t>AZRA HAIFA AURA PUTRI</t>
+  </si>
+  <si>
+    <t>BELVA HUWALDA CARISSA</t>
+  </si>
+  <si>
+    <t>FARHAN JEZANDO WARDANA</t>
+  </si>
+  <si>
+    <t>Nama Klub / PB</t>
+  </si>
+  <si>
+    <t>ARJUNA KUTAI KARTANEGARA</t>
+  </si>
+  <si>
+    <t>HEVINDO BALIKPAPAN</t>
+  </si>
+  <si>
+    <t>PB DJARUM</t>
+  </si>
+  <si>
+    <t>PB JAYA RAYA</t>
+  </si>
+  <si>
+    <t>Nama Wasit</t>
+  </si>
+  <si>
+    <t>Agam</t>
+  </si>
+  <si>
+    <t>Anis Firdaus</t>
+  </si>
+  <si>
+    <t>Annes Faisal</t>
+  </si>
+  <si>
+    <t>Dian Asrori</t>
+  </si>
+  <si>
+    <t>Ferry Anggriawan</t>
+  </si>
+  <si>
+    <t>Fikri</t>
+  </si>
+  <si>
+    <t>Furqon</t>
+  </si>
+  <si>
+    <t>Lucky Zulkarnain</t>
+  </si>
+  <si>
+    <t>Ndari Wahyu</t>
+  </si>
+  <si>
+    <t>Robi Wisnu</t>
+  </si>
+  <si>
+    <t>Ronny Azhari</t>
+  </si>
+  <si>
+    <t>Wardana</t>
+  </si>
+  <si>
+    <t>Nama Service Judge</t>
+  </si>
+  <si>
+    <t>Ali</t>
+  </si>
+  <si>
+    <t>Alis</t>
+  </si>
+  <si>
+    <t>Alwi</t>
+  </si>
+  <si>
+    <t>Arifin</t>
+  </si>
+  <si>
+    <t>Badarudin</t>
+  </si>
+  <si>
+    <t>Gagah</t>
+  </si>
+  <si>
+    <t>Haris</t>
+  </si>
+  <si>
+    <t>Hermawan</t>
+  </si>
+  <si>
+    <t>Iban</t>
+  </si>
+  <si>
+    <t>Lukman</t>
+  </si>
+  <si>
+    <t>Nanang</t>
+  </si>
+  <si>
+    <t>Rudi</t>
+  </si>
+  <si>
+    <t>Samsul</t>
+  </si>
+  <si>
+    <t>Septian</t>
+  </si>
+  <si>
+    <t>Syafi'i</t>
+  </si>
+  <si>
+    <t>Yusri</t>
+  </si>
+  <si>
+    <t>Nama Turnamen</t>
+  </si>
+  <si>
+    <t>Nama Lapangan</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>No. Partai</t>
+  </si>
+  <si>
+    <t>QF-1</t>
+  </si>
+  <si>
+    <t>SF-1</t>
+  </si>
+  <si>
+    <t>Pupuk Kaltim Open 2026 (Gor Alamanda)</t>
+  </si>
+  <si>
+    <t>Pupuk Kaltim Open 2026 (Gor Graha Cipta Korsa)</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-  </numFmts>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -71,13 +218,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -402,338 +557,352 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:A6"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.5"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Nama Pemain</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>ALISA AMELIA DANSACH</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>ALYA MUHKBITA SARI</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>AZRA HAIFA AURA PUTRI</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>BELVA HUWALDA CARISSA</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>FARHAN JEZANDO WARDANA</v>
+    <row r="1" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="A6" t="s">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:A6"/>
+    <ignoredError sqref="A1:A6" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:A5"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.5"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Nama Klub / PB</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>ARJUNA KUTAI KARTANEGARA</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>HEVINDO BALIKPAPAN</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>PB DJARUM</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>PB JAYA RAYA</v>
+    <row r="1" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="A1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="A2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="A4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="A5" t="s">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:A5"/>
+    <ignoredError sqref="A1:A5" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:A13"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.5"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Nama Wasit</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>Agam</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>Anis Firdaus</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>Annes Faisal</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>Dian Asrori</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>Ferry Anggriawan</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>Fikri</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>Furqon</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>Lucky Zulkarnain</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>Ndari Wahyu</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>Robi Wisnu</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>Ronny Azhari</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>Wardana</v>
+    <row r="1" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="A1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="A2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="A3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="A4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="A5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="A6" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="A7" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="A8" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="A9" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="A10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="A11" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="A12" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="A13" t="s">
+        <v>23</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:A13"/>
+    <ignoredError sqref="A1:A13" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:A17"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.5"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Nama Service Judge</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>Ali</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>Alis</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>Alwi</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>Arifin</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>Badarudin</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>Gagah</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>Haris</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>Hermawan</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>Iban</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>Lukman</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>Nanang</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>Rudi</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>Samsul</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>Septian</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>Syafi'i</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="str">
-        <v>Yusri</v>
+    <row r="1" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="A1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="A2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="A3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="A4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="A5" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="A6" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="A7" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="A8" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="A9" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="A10" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="A11" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="A12" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="A13" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="A14" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="A15" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="A16" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="A17" t="s">
+        <v>40</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:A17"/>
+    <ignoredError sqref="A1:A17" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:A3"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.5"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Nama Turnamen</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>Pupuk Kaltim Open 2026: Gor Alamanda</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>Pupuk Kaltim Open 2026: Gor Graha Cipta Korsa</v>
+    <row r="1" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="A1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="A2" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="A3" t="s">
+        <v>51</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:A3"/>
+    <ignoredError sqref="A1" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:A5"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.5"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Nama Lapangan</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>4</v>
+    <row r="1" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="A1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="A2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="A3" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="A4" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="A5" t="s">
+        <v>46</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:A5"/>
+    <ignoredError sqref="A1:A5" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:A3"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.5"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>No. Partai</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>QF-1</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>SF-1</v>
+    <row r="1" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="A1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="A2" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="A3" t="s">
+        <v>49</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:A3"/>
+    <ignoredError sqref="A1:A3" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>